--- a/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-24T16:30:00+00:00</t>
+    <t>2025-10-28T16:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T16:16:24+00:00</t>
+    <t>2025-10-28T18:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T18:01:21+00:00</t>
+    <t>2025-10-28T19:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T19:18:48+00:00</t>
+    <t>2025-10-29T09:26:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-29T09:26:27+00:00</t>
+    <t>2025-10-29T12:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-29T12:44:38+00:00</t>
+    <t>2025-10-30T12:13:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
+++ b/ig/TEST-SUPPLEMENT/ValueSet-jdv-modele-document-cda.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T12:13:43+00:00</t>
+    <t>2025-11-09T13:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
